--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119844195</v>
+        <v>119838814</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,45 +4506,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491210</v>
+        <v>491028</v>
       </c>
       <c r="R36" t="n">
-        <v>6942900</v>
+        <v>6943013</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4571,14 +4563,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119838814</v>
+        <v>119844195</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4621,37 +4618,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491028</v>
+        <v>491210</v>
       </c>
       <c r="R37" t="n">
-        <v>6943013</v>
+        <v>6942900</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4678,19 +4683,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:44</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -3685,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119840374</v>
+        <v>119844232</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,37 +3701,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490963</v>
+        <v>491042</v>
       </c>
       <c r="R29" t="n">
-        <v>6943253</v>
+        <v>6942994</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3758,19 +3766,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>19:08</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119844232</v>
+        <v>119840374</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3813,45 +3816,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491042</v>
+        <v>490963</v>
       </c>
       <c r="R30" t="n">
-        <v>6942994</v>
+        <v>6943253</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3878,14 +3873,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,7 +2441,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119838719</v>
+        <v>119838566</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491033</v>
+        <v>491070</v>
       </c>
       <c r="R18" t="n">
-        <v>6943021</v>
+        <v>6942988</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119836355</v>
+        <v>119839540</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,34 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491146</v>
+        <v>490872</v>
       </c>
       <c r="R19" t="n">
-        <v>6942933</v>
+        <v>6943080</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119834113</v>
+        <v>119836510</v>
       </c>
       <c r="B20" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,38 +2686,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491239</v>
+        <v>491143</v>
       </c>
       <c r="R20" t="n">
-        <v>6942931</v>
+        <v>6942954</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2749,7 +2758,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2759,7 +2768,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,10 +2795,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119834166</v>
+        <v>119837487</v>
       </c>
       <c r="B21" t="n">
-        <v>74638</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,21 +2811,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491238</v>
+        <v>491110</v>
       </c>
       <c r="R21" t="n">
-        <v>6942925</v>
+        <v>6942959</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2861,7 +2870,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2880,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,10 +2907,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839776</v>
+        <v>119840374</v>
       </c>
       <c r="B22" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,50 +2919,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490825</v>
+        <v>490963</v>
       </c>
       <c r="R22" t="n">
-        <v>6943132</v>
+        <v>6943253</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119844150</v>
+        <v>119839776</v>
       </c>
       <c r="B23" t="n">
-        <v>78263</v>
+        <v>56522</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3031,44 +3031,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491277</v>
+        <v>490825</v>
       </c>
       <c r="R23" t="n">
-        <v>6942954</v>
+        <v>6943132</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3095,18 +3101,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3125,7 +3140,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119835443</v>
+        <v>119834064</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3161,14 +3176,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491200</v>
+        <v>491239</v>
       </c>
       <c r="R24" t="n">
-        <v>6942933</v>
+        <v>6942931</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3200,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,7 +3225,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119834815</v>
+        <v>119844150</v>
       </c>
       <c r="B25" t="n">
-        <v>74638</v>
+        <v>78263</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,37 +3268,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491212</v>
+        <v>491277</v>
       </c>
       <c r="R25" t="n">
-        <v>6942907</v>
+        <v>6942954</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,27 +3328,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3349,10 +3358,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834398</v>
+        <v>119836355</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,21 +3374,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3389,10 +3398,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491234</v>
+        <v>491146</v>
       </c>
       <c r="R26" t="n">
-        <v>6942911</v>
+        <v>6942933</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3424,7 +3433,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3434,7 +3443,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,10 +3470,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119837487</v>
+        <v>119834166</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,21 +3486,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3501,10 +3510,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491110</v>
+        <v>491238</v>
       </c>
       <c r="R27" t="n">
-        <v>6942959</v>
+        <v>6942925</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3536,7 +3545,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3546,7 +3555,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3573,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834064</v>
+        <v>119834815</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,34 +3598,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491239</v>
+        <v>491212</v>
       </c>
       <c r="R28" t="n">
-        <v>6942931</v>
+        <v>6942907</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3648,7 +3657,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3658,7 +3667,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3685,10 +3694,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119844232</v>
+        <v>119834398</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>74638</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,45 +3710,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491042</v>
+        <v>491234</v>
       </c>
       <c r="R29" t="n">
-        <v>6942994</v>
+        <v>6942911</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3766,14 +3767,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,10 +3806,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119840374</v>
+        <v>119834113</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,34 +3822,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490963</v>
+        <v>491239</v>
       </c>
       <c r="R30" t="n">
-        <v>6943253</v>
+        <v>6942931</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3875,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3885,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839540</v>
+        <v>119844195</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3928,37 +3934,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490872</v>
+        <v>491210</v>
       </c>
       <c r="R31" t="n">
-        <v>6943080</v>
+        <v>6942900</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3985,19 +3999,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:33</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4024,10 +4033,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119836510</v>
+        <v>119844232</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4036,50 +4045,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491143</v>
+        <v>491042</v>
       </c>
       <c r="R32" t="n">
-        <v>6942954</v>
+        <v>6942994</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,19 +4114,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:01</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119836200</v>
+        <v>119838814</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4161,34 +4164,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491170</v>
+        <v>491028</v>
       </c>
       <c r="R33" t="n">
-        <v>6942951</v>
+        <v>6943013</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4220,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4230,7 +4233,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4257,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119834531</v>
+        <v>119835443</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4269,47 +4272,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491220</v>
+        <v>491200</v>
       </c>
       <c r="R34" t="n">
-        <v>6942907</v>
+        <v>6942933</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4345,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4372,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840179</v>
+        <v>119844174</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,41 +4384,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490932</v>
+        <v>491221</v>
       </c>
       <c r="R35" t="n">
-        <v>6943156</v>
+        <v>6942905</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4451,19 +4453,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>18:57</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4487,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119838814</v>
+        <v>119839263</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,34 +4503,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491028</v>
+        <v>490923</v>
       </c>
       <c r="R36" t="n">
-        <v>6943013</v>
+        <v>6943060</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4565,7 +4562,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4572,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,7 +4599,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119844195</v>
+        <v>119844215</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4650,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491210</v>
+        <v>491220</v>
       </c>
       <c r="R37" t="n">
-        <v>6942900</v>
+        <v>6942894</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4717,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119844215</v>
+        <v>119838719</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4729,49 +4726,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491220</v>
+        <v>491033</v>
       </c>
       <c r="R38" t="n">
-        <v>6942894</v>
+        <v>6943021</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4798,14 +4796,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844174</v>
+        <v>119840179</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4844,49 +4847,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491221</v>
+        <v>490932</v>
       </c>
       <c r="R39" t="n">
-        <v>6942905</v>
+        <v>6943156</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4913,14 +4908,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119839263</v>
+        <v>119834531</v>
       </c>
       <c r="B40" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,38 +4959,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490923</v>
+        <v>491220</v>
       </c>
       <c r="R40" t="n">
-        <v>6943060</v>
+        <v>6942907</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5022,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5032,7 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5059,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119838566</v>
+        <v>119836200</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,47 +5080,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491070</v>
+        <v>491170</v>
       </c>
       <c r="R41" t="n">
-        <v>6942988</v>
+        <v>6942951</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -3252,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119844150</v>
+        <v>119844195</v>
       </c>
       <c r="B25" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,26 +3268,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3295,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491277</v>
+        <v>491210</v>
       </c>
       <c r="R25" t="n">
-        <v>6942954</v>
+        <v>6942900</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,13 +3338,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3358,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119836355</v>
+        <v>119834166</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3374,21 +3383,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491146</v>
+        <v>491238</v>
       </c>
       <c r="R26" t="n">
-        <v>6942933</v>
+        <v>6942925</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3433,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3443,7 +3452,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,7 +3479,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834166</v>
+        <v>119834815</v>
       </c>
       <c r="B27" t="n">
         <v>74638</v>
@@ -3510,10 +3519,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491238</v>
+        <v>491212</v>
       </c>
       <c r="R27" t="n">
-        <v>6942925</v>
+        <v>6942907</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3545,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3555,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,7 +3591,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834815</v>
+        <v>119834398</v>
       </c>
       <c r="B28" t="n">
         <v>74638</v>
@@ -3622,10 +3631,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491212</v>
+        <v>491234</v>
       </c>
       <c r="R28" t="n">
-        <v>6942907</v>
+        <v>6942911</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3657,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3667,7 +3676,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,7 +3703,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834398</v>
+        <v>119834113</v>
       </c>
       <c r="B29" t="n">
         <v>74638</v>
@@ -3734,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491234</v>
+        <v>491239</v>
       </c>
       <c r="R29" t="n">
-        <v>6942911</v>
+        <v>6942931</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3769,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3788,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119834113</v>
+        <v>119836355</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3822,21 +3831,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3855,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491239</v>
+        <v>491146</v>
       </c>
       <c r="R30" t="n">
-        <v>6942931</v>
+        <v>6942933</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3881,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119844195</v>
+        <v>119844150</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,31 +3943,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3966,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491210</v>
+        <v>491277</v>
       </c>
       <c r="R31" t="n">
-        <v>6942900</v>
+        <v>6942954</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4004,17 +4008,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119838814</v>
+        <v>119835443</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,34 +4164,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491028</v>
+        <v>491200</v>
       </c>
       <c r="R33" t="n">
-        <v>6943013</v>
+        <v>6942933</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119835443</v>
+        <v>119844174</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,37 +4276,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491200</v>
+        <v>491221</v>
       </c>
       <c r="R34" t="n">
-        <v>6942933</v>
+        <v>6942905</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4333,19 +4341,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119844174</v>
+        <v>119838814</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,45 +4391,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491221</v>
+        <v>491028</v>
       </c>
       <c r="R35" t="n">
-        <v>6942905</v>
+        <v>6943013</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,14 +4448,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,7 +2441,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119838566</v>
+        <v>119836510</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2486,14 +2486,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491070</v>
+        <v>491143</v>
       </c>
       <c r="R18" t="n">
-        <v>6942988</v>
+        <v>6942954</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839540</v>
+        <v>119840374</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,34 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490872</v>
+        <v>490963</v>
       </c>
       <c r="R19" t="n">
-        <v>6943080</v>
+        <v>6943253</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119836510</v>
+        <v>119834815</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,47 +2686,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491143</v>
+        <v>491212</v>
       </c>
       <c r="R20" t="n">
-        <v>6942954</v>
+        <v>6942907</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2758,7 +2749,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2768,7 +2759,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119837487</v>
+        <v>119836355</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,21 +2802,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491110</v>
+        <v>491146</v>
       </c>
       <c r="R21" t="n">
-        <v>6942959</v>
+        <v>6942933</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2870,7 +2861,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2880,7 +2871,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840374</v>
+        <v>119839540</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2923,34 +2914,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490963</v>
+        <v>490872</v>
       </c>
       <c r="R22" t="n">
-        <v>6943253</v>
+        <v>6943080</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2982,7 +2973,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2992,7 +2983,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839776</v>
+        <v>119844195</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3031,50 +3022,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490825</v>
+        <v>491210</v>
       </c>
       <c r="R23" t="n">
-        <v>6943132</v>
+        <v>6942900</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,19 +3091,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>18:40</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119834064</v>
+        <v>119834531</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3152,38 +3137,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491239</v>
+        <v>491220</v>
       </c>
       <c r="R24" t="n">
-        <v>6942931</v>
+        <v>6942907</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3215,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,7 +3246,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119844195</v>
+        <v>119844174</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3300,10 +3294,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491210</v>
+        <v>491221</v>
       </c>
       <c r="R25" t="n">
-        <v>6942900</v>
+        <v>6942905</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3479,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834815</v>
+        <v>119844150</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>78263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3495,37 +3489,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491212</v>
+        <v>491277</v>
       </c>
       <c r="R27" t="n">
-        <v>6942907</v>
+        <v>6942954</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3552,27 +3549,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3591,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834398</v>
+        <v>119839776</v>
       </c>
       <c r="B28" t="n">
-        <v>74638</v>
+        <v>56522</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,41 +3591,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491234</v>
+        <v>490825</v>
       </c>
       <c r="R28" t="n">
-        <v>6942911</v>
+        <v>6943132</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3666,7 +3663,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,7 +3673,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834113</v>
+        <v>119835443</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,21 +3716,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3743,10 +3740,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491239</v>
+        <v>491200</v>
       </c>
       <c r="R29" t="n">
-        <v>6942931</v>
+        <v>6942933</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3778,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3788,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119836355</v>
+        <v>119839263</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>74638</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,34 +3828,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491146</v>
+        <v>490923</v>
       </c>
       <c r="R30" t="n">
-        <v>6942933</v>
+        <v>6943060</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3890,7 +3887,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3897,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,10 +3924,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119844150</v>
+        <v>119834064</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3943,40 +3940,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491277</v>
+        <v>491239</v>
       </c>
       <c r="R31" t="n">
-        <v>6942954</v>
+        <v>6942931</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4003,18 +3997,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +4036,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119844232</v>
+        <v>119834113</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>74638</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,45 +4052,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491042</v>
+        <v>491239</v>
       </c>
       <c r="R32" t="n">
-        <v>6942994</v>
+        <v>6942931</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4114,14 +4109,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119835443</v>
+        <v>119836200</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491200</v>
+        <v>491170</v>
       </c>
       <c r="R33" t="n">
-        <v>6942933</v>
+        <v>6942951</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119844174</v>
+        <v>119838566</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,49 +4272,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491221</v>
+        <v>491070</v>
       </c>
       <c r="R34" t="n">
-        <v>6942905</v>
+        <v>6942988</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4341,14 +4342,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119838814</v>
+        <v>119840179</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,25 +4393,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4415,10 +4421,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491028</v>
+        <v>490932</v>
       </c>
       <c r="R35" t="n">
-        <v>6943013</v>
+        <v>6943156</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4450,7 +4456,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4466,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119839263</v>
+        <v>119844232</v>
       </c>
       <c r="B36" t="n">
-        <v>74638</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4503,37 +4509,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490923</v>
+        <v>491042</v>
       </c>
       <c r="R36" t="n">
-        <v>6943060</v>
+        <v>6942994</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4560,19 +4574,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:22</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:22</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119844215</v>
+        <v>119838719</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,49 +4620,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491220</v>
+        <v>491033</v>
       </c>
       <c r="R37" t="n">
-        <v>6942894</v>
+        <v>6943021</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4680,14 +4690,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838719</v>
+        <v>119837487</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4726,47 +4741,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491033</v>
+        <v>491110</v>
       </c>
       <c r="R38" t="n">
-        <v>6943021</v>
+        <v>6942959</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4798,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4808,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119840179</v>
+        <v>119838814</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,25 +4853,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4875,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490932</v>
+        <v>491028</v>
       </c>
       <c r="R39" t="n">
-        <v>6943156</v>
+        <v>6943013</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4910,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4920,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4947,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119834531</v>
+        <v>119844215</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,50 +4965,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
         <v>491220</v>
       </c>
       <c r="R40" t="n">
-        <v>6942907</v>
+        <v>6942894</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,19 +5034,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119836200</v>
+        <v>119834398</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5084,21 +5084,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491170</v>
+        <v>491234</v>
       </c>
       <c r="R41" t="n">
-        <v>6942951</v>
+        <v>6942911</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -3473,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119844150</v>
+        <v>119839776</v>
       </c>
       <c r="B27" t="n">
-        <v>78263</v>
+        <v>56522</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,44 +3485,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491277</v>
+        <v>490825</v>
       </c>
       <c r="R27" t="n">
-        <v>6942954</v>
+        <v>6943132</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,18 +3555,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839776</v>
+        <v>119844150</v>
       </c>
       <c r="B28" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,50 +3606,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490825</v>
+        <v>491277</v>
       </c>
       <c r="R28" t="n">
-        <v>6943132</v>
+        <v>6942954</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,27 +3670,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119838719</v>
+        <v>119837487</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,47 +4620,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491033</v>
+        <v>491110</v>
       </c>
       <c r="R37" t="n">
-        <v>6943021</v>
+        <v>6942959</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4692,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,7 +4720,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837487</v>
+        <v>119838814</v>
       </c>
       <c r="B38" t="n">
         <v>79607</v>
@@ -4765,14 +4756,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491110</v>
+        <v>491028</v>
       </c>
       <c r="R38" t="n">
-        <v>6942959</v>
+        <v>6943013</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4804,7 +4795,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4805,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119838814</v>
+        <v>119844215</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4857,37 +4848,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491028</v>
+        <v>491220</v>
       </c>
       <c r="R39" t="n">
-        <v>6943013</v>
+        <v>6942894</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4914,19 +4913,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:44</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119844215</v>
+        <v>119838719</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4965,49 +4959,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491220</v>
+        <v>491033</v>
       </c>
       <c r="R40" t="n">
-        <v>6942894</v>
+        <v>6943021</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5034,14 +5029,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119836510</v>
+        <v>119834815</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,47 +2453,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491143</v>
+        <v>491212</v>
       </c>
       <c r="R18" t="n">
-        <v>6942954</v>
+        <v>6942907</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2525,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2535,7 +2526,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840374</v>
+        <v>119839540</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,34 +2569,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490963</v>
+        <v>490872</v>
       </c>
       <c r="R19" t="n">
-        <v>6943253</v>
+        <v>6943080</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2637,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2647,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119834815</v>
+        <v>119834166</v>
       </c>
       <c r="B20" t="n">
         <v>74638</v>
@@ -2714,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491212</v>
+        <v>491238</v>
       </c>
       <c r="R20" t="n">
-        <v>6942907</v>
+        <v>6942925</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2749,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2759,7 +2750,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,10 +2777,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119836355</v>
+        <v>119837487</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2802,21 +2793,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2826,10 +2817,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491146</v>
+        <v>491110</v>
       </c>
       <c r="R21" t="n">
-        <v>6942933</v>
+        <v>6942959</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2861,7 +2852,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2871,7 +2862,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839540</v>
+        <v>119839263</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,21 +2905,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490872</v>
+        <v>490923</v>
       </c>
       <c r="R22" t="n">
-        <v>6943080</v>
+        <v>6943060</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2973,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119844195</v>
+        <v>119838566</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3022,49 +3013,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491210</v>
+        <v>491070</v>
       </c>
       <c r="R23" t="n">
-        <v>6942900</v>
+        <v>6942988</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3091,14 +3083,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119834531</v>
+        <v>119844215</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3137,50 +3134,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
         <v>491220</v>
       </c>
       <c r="R24" t="n">
-        <v>6942907</v>
+        <v>6942894</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3207,19 +3203,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119844174</v>
+        <v>119834398</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>74638</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3262,45 +3253,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491221</v>
+        <v>491234</v>
       </c>
       <c r="R25" t="n">
-        <v>6942905</v>
+        <v>6942911</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3327,14 +3310,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834166</v>
+        <v>119836355</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3377,21 +3365,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491238</v>
+        <v>491146</v>
       </c>
       <c r="R26" t="n">
-        <v>6942925</v>
+        <v>6942933</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3436,7 +3424,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3434,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,10 +3461,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839776</v>
+        <v>119844150</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,50 +3473,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490825</v>
+        <v>491277</v>
       </c>
       <c r="R27" t="n">
-        <v>6943132</v>
+        <v>6942954</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,27 +3537,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3594,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119844150</v>
+        <v>119844174</v>
       </c>
       <c r="B28" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3610,26 +3583,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3637,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491277</v>
+        <v>491221</v>
       </c>
       <c r="R28" t="n">
-        <v>6942954</v>
+        <v>6942905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,13 +3653,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3700,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119835443</v>
+        <v>119834113</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,21 +3698,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,10 +3722,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491200</v>
+        <v>491239</v>
       </c>
       <c r="R29" t="n">
-        <v>6942933</v>
+        <v>6942931</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3775,7 +3757,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3767,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,10 +3794,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839263</v>
+        <v>119834531</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,38 +3806,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490923</v>
+        <v>491220</v>
       </c>
       <c r="R30" t="n">
-        <v>6943060</v>
+        <v>6942907</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3887,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3897,7 +3888,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,7 +3915,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119834064</v>
+        <v>119835443</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3960,14 +3951,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491239</v>
+        <v>491200</v>
       </c>
       <c r="R31" t="n">
-        <v>6942931</v>
+        <v>6942933</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3999,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4009,7 +4000,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4036,10 +4027,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119834113</v>
+        <v>119844195</v>
       </c>
       <c r="B32" t="n">
-        <v>74638</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4052,37 +4043,45 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491239</v>
+        <v>491210</v>
       </c>
       <c r="R32" t="n">
-        <v>6942931</v>
+        <v>6942900</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4109,19 +4108,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:03</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4148,7 +4142,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119836200</v>
+        <v>119834064</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4184,14 +4178,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491170</v>
+        <v>491239</v>
       </c>
       <c r="R33" t="n">
-        <v>6942951</v>
+        <v>6942931</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4223,7 +4217,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4233,7 +4227,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,7 +4254,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119838566</v>
+        <v>119836510</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4295,7 +4289,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4305,14 +4299,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491070</v>
+        <v>491143</v>
       </c>
       <c r="R34" t="n">
-        <v>6942988</v>
+        <v>6942954</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4344,7 +4338,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4348,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840179</v>
+        <v>119836200</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,38 +4387,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490932</v>
+        <v>491170</v>
       </c>
       <c r="R35" t="n">
-        <v>6943156</v>
+        <v>6942951</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4456,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4487,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119844232</v>
+        <v>119840374</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,45 +4503,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491042</v>
+        <v>490963</v>
       </c>
       <c r="R36" t="n">
-        <v>6942994</v>
+        <v>6943253</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4574,14 +4560,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,10 +4599,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119837487</v>
+        <v>119839776</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>56522</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,41 +4611,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491110</v>
+        <v>490825</v>
       </c>
       <c r="R37" t="n">
-        <v>6942959</v>
+        <v>6943132</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838814</v>
+        <v>119838719</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,38 +4732,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491028</v>
+        <v>491033</v>
       </c>
       <c r="R38" t="n">
-        <v>6943013</v>
+        <v>6943021</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4795,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,7 +4841,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844215</v>
+        <v>119844232</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4880,10 +4889,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491220</v>
+        <v>491042</v>
       </c>
       <c r="R39" t="n">
-        <v>6942894</v>
+        <v>6942994</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4947,10 +4956,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119838719</v>
+        <v>119838814</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,47 +4968,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491033</v>
+        <v>491028</v>
       </c>
       <c r="R40" t="n">
-        <v>6943021</v>
+        <v>6943013</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119834398</v>
+        <v>119840179</v>
       </c>
       <c r="B41" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,38 +5080,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491234</v>
+        <v>490932</v>
       </c>
       <c r="R41" t="n">
-        <v>6942911</v>
+        <v>6943156</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2889,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839263</v>
+        <v>119838566</v>
       </c>
       <c r="B22" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,38 +2901,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490923</v>
+        <v>491070</v>
       </c>
       <c r="R22" t="n">
-        <v>6943060</v>
+        <v>6942988</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2964,7 +2973,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2974,7 +2983,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119838566</v>
+        <v>119839263</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,47 +3022,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491070</v>
+        <v>490923</v>
       </c>
       <c r="R23" t="n">
-        <v>6942988</v>
+        <v>6943060</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838719</v>
+        <v>119844232</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,50 +4732,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491033</v>
+        <v>491042</v>
       </c>
       <c r="R38" t="n">
-        <v>6943021</v>
+        <v>6942994</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4802,19 +4801,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844232</v>
+        <v>119838719</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,49 +4847,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491042</v>
+        <v>491033</v>
       </c>
       <c r="R39" t="n">
-        <v>6942994</v>
+        <v>6943021</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4922,14 +4917,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2889,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838566</v>
+        <v>119839263</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,47 +2901,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491070</v>
+        <v>490923</v>
       </c>
       <c r="R22" t="n">
-        <v>6942988</v>
+        <v>6943060</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2973,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839263</v>
+        <v>119838566</v>
       </c>
       <c r="B23" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3022,38 +3013,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490923</v>
+        <v>491070</v>
       </c>
       <c r="R23" t="n">
-        <v>6943060</v>
+        <v>6942988</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119844232</v>
+        <v>119838719</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,49 +4732,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491042</v>
+        <v>491033</v>
       </c>
       <c r="R38" t="n">
-        <v>6942994</v>
+        <v>6943021</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4801,14 +4802,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119838719</v>
+        <v>119844232</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,50 +4853,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491033</v>
+        <v>491042</v>
       </c>
       <c r="R39" t="n">
-        <v>6943021</v>
+        <v>6942994</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,19 +4922,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839540</v>
+        <v>119834166</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>74638</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,34 +2569,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490872</v>
+        <v>491238</v>
       </c>
       <c r="R19" t="n">
-        <v>6943080</v>
+        <v>6942925</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119834166</v>
+        <v>119839540</v>
       </c>
       <c r="B20" t="n">
-        <v>74638</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,34 +2681,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491238</v>
+        <v>490872</v>
       </c>
       <c r="R20" t="n">
-        <v>6942925</v>
+        <v>6943080</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838719</v>
+        <v>119844232</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,50 +4732,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491033</v>
+        <v>491042</v>
       </c>
       <c r="R38" t="n">
-        <v>6943021</v>
+        <v>6942994</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4802,19 +4801,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844232</v>
+        <v>119838719</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,49 +4847,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491042</v>
+        <v>491033</v>
       </c>
       <c r="R39" t="n">
-        <v>6942994</v>
+        <v>6943021</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4922,14 +4917,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2889,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839263</v>
+        <v>119838566</v>
       </c>
       <c r="B22" t="n">
-        <v>74638</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,38 +2901,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490923</v>
+        <v>491070</v>
       </c>
       <c r="R22" t="n">
-        <v>6943060</v>
+        <v>6942988</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2964,7 +2973,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2974,7 +2983,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119838566</v>
+        <v>119839263</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>74638</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,47 +3022,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491070</v>
+        <v>490923</v>
       </c>
       <c r="R23" t="n">
-        <v>6942988</v>
+        <v>6943060</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834815</v>
+        <v>119835443</v>
       </c>
       <c r="B18" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491212</v>
+        <v>491200</v>
       </c>
       <c r="R18" t="n">
-        <v>6942907</v>
+        <v>6942933</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119834166</v>
+        <v>119834815</v>
       </c>
       <c r="B19" t="n">
-        <v>74638</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491238</v>
+        <v>491212</v>
       </c>
       <c r="R19" t="n">
-        <v>6942925</v>
+        <v>6942907</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839540</v>
+        <v>119844150</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>78279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,37 +2681,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490872</v>
+        <v>491277</v>
       </c>
       <c r="R20" t="n">
-        <v>6943080</v>
+        <v>6942954</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2738,27 +2741,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2777,10 +2771,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119837487</v>
+        <v>119838566</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,38 +2783,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491110</v>
+        <v>491070</v>
       </c>
       <c r="R21" t="n">
-        <v>6942959</v>
+        <v>6942988</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2852,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838566</v>
+        <v>119838719</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,10 +2941,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491070</v>
+        <v>491033</v>
       </c>
       <c r="R22" t="n">
-        <v>6942988</v>
+        <v>6943021</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2973,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,10 +3013,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839263</v>
+        <v>119834398</v>
       </c>
       <c r="B23" t="n">
-        <v>74638</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,14 +3049,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490923</v>
+        <v>491234</v>
       </c>
       <c r="R23" t="n">
-        <v>6943060</v>
+        <v>6942911</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3085,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3095,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119844215</v>
+        <v>119839263</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3138,45 +3141,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491220</v>
+        <v>490923</v>
       </c>
       <c r="R24" t="n">
-        <v>6942894</v>
+        <v>6943060</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,14 +3198,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119834398</v>
+        <v>119840374</v>
       </c>
       <c r="B25" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,34 +3253,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491234</v>
+        <v>490963</v>
       </c>
       <c r="R25" t="n">
-        <v>6942911</v>
+        <v>6943253</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3349,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119836355</v>
+        <v>119836200</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491146</v>
+        <v>491170</v>
       </c>
       <c r="R26" t="n">
-        <v>6942933</v>
+        <v>6942951</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119844150</v>
+        <v>119837487</v>
       </c>
       <c r="B27" t="n">
-        <v>78263</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,40 +3477,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491277</v>
+        <v>491110</v>
       </c>
       <c r="R27" t="n">
-        <v>6942954</v>
+        <v>6942959</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,18 +3534,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3567,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119844174</v>
+        <v>119834113</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>74654</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,45 +3589,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491221</v>
+        <v>491239</v>
       </c>
       <c r="R28" t="n">
-        <v>6942905</v>
+        <v>6942931</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3648,14 +3646,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3682,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834113</v>
+        <v>119836355</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3698,21 +3701,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3722,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491239</v>
+        <v>491146</v>
       </c>
       <c r="R29" t="n">
-        <v>6942931</v>
+        <v>6942933</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3757,7 +3760,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3767,7 +3770,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3794,10 +3797,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119834531</v>
+        <v>119844174</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,50 +3809,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491220</v>
+        <v>491221</v>
       </c>
       <c r="R30" t="n">
-        <v>6942907</v>
+        <v>6942905</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,19 +3878,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3915,10 +3912,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835443</v>
+        <v>119836510</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3927,38 +3924,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491200</v>
+        <v>491143</v>
       </c>
       <c r="R31" t="n">
-        <v>6942933</v>
+        <v>6942954</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3990,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4000,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,10 +4033,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119844195</v>
+        <v>119839776</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>56532</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4039,49 +4045,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491210</v>
+        <v>490825</v>
       </c>
       <c r="R32" t="n">
-        <v>6942900</v>
+        <v>6943132</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4108,14 +4115,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119834064</v>
+        <v>119834166</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>74654</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4158,34 +4170,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491239</v>
+        <v>491238</v>
       </c>
       <c r="R33" t="n">
-        <v>6942931</v>
+        <v>6942925</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4217,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4227,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4254,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119836510</v>
+        <v>119839540</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4266,47 +4278,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491143</v>
+        <v>490872</v>
       </c>
       <c r="R34" t="n">
-        <v>6942954</v>
+        <v>6943080</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4338,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4348,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119836200</v>
+        <v>119844215</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,37 +4394,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491170</v>
+        <v>491220</v>
       </c>
       <c r="R35" t="n">
-        <v>6942951</v>
+        <v>6942894</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4448,19 +4459,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:43</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119840374</v>
+        <v>119840179</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,25 +4505,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4527,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490963</v>
+        <v>490932</v>
       </c>
       <c r="R36" t="n">
-        <v>6943253</v>
+        <v>6943156</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4562,7 +4568,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4572,7 +4578,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4599,10 +4605,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119839776</v>
+        <v>119838814</v>
       </c>
       <c r="B37" t="n">
-        <v>56522</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,50 +4617,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490825</v>
+        <v>491028</v>
       </c>
       <c r="R37" t="n">
-        <v>6943132</v>
+        <v>6943013</v>
       </c>
       <c r="S37" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,7 +4680,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4690,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4723,7 +4720,7 @@
         <v>119844232</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4835,10 +4832,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119838719</v>
+        <v>119834531</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4880,14 +4877,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491033</v>
+        <v>491220</v>
       </c>
       <c r="R39" t="n">
-        <v>6943021</v>
+        <v>6942907</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4919,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4956,10 +4953,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119838814</v>
+        <v>119844195</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4972,37 +4969,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491028</v>
+        <v>491210</v>
       </c>
       <c r="R40" t="n">
-        <v>6943013</v>
+        <v>6942900</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,19 +5034,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:44</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119840179</v>
+        <v>119834064</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,38 +5080,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490932</v>
+        <v>491239</v>
       </c>
       <c r="R41" t="n">
-        <v>6943156</v>
+        <v>6942931</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -4605,10 +4605,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119838814</v>
+        <v>119834531</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4617,38 +4617,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491028</v>
+        <v>491220</v>
       </c>
       <c r="R37" t="n">
-        <v>6943013</v>
+        <v>6942907</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4680,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4690,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,10 +4726,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119844232</v>
+        <v>119838814</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,45 +4742,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491042</v>
+        <v>491028</v>
       </c>
       <c r="R38" t="n">
-        <v>6942994</v>
+        <v>6943013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4798,14 +4799,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4832,10 +4838,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119834531</v>
+        <v>119844232</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4844,50 +4850,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491220</v>
+        <v>491042</v>
       </c>
       <c r="R39" t="n">
-        <v>6942907</v>
+        <v>6942994</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4914,19 +4919,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119835443</v>
+        <v>119844195</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,37 +2457,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491200</v>
+        <v>491210</v>
       </c>
       <c r="R18" t="n">
-        <v>6942933</v>
+        <v>6942900</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,19 +2522,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119834815</v>
+        <v>119836355</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,21 +2572,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491212</v>
+        <v>491146</v>
       </c>
       <c r="R19" t="n">
-        <v>6942907</v>
+        <v>6942933</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2628,7 +2631,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2641,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2668,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119844150</v>
+        <v>119834531</v>
       </c>
       <c r="B20" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,44 +2680,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491277</v>
+        <v>491220</v>
       </c>
       <c r="R20" t="n">
-        <v>6942954</v>
+        <v>6942907</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,18 +2750,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2771,7 +2789,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119838566</v>
+        <v>119836510</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2806,7 +2824,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2816,14 +2834,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491070</v>
+        <v>491143</v>
       </c>
       <c r="R21" t="n">
-        <v>6942988</v>
+        <v>6942954</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2855,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2883,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,10 +2910,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838719</v>
+        <v>119840179</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,47 +2922,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491033</v>
+        <v>490932</v>
       </c>
       <c r="R22" t="n">
-        <v>6943021</v>
+        <v>6943156</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2976,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119834398</v>
+        <v>119839776</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>56532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3025,41 +3034,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491234</v>
+        <v>490825</v>
       </c>
       <c r="R23" t="n">
-        <v>6942911</v>
+        <v>6943132</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839263</v>
+        <v>119835443</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3141,34 +3159,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490923</v>
+        <v>491200</v>
       </c>
       <c r="R24" t="n">
-        <v>6943060</v>
+        <v>6942933</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3200,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119840374</v>
+        <v>119834113</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,34 +3271,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490963</v>
+        <v>491239</v>
       </c>
       <c r="R25" t="n">
-        <v>6943253</v>
+        <v>6942931</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3312,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3322,7 +3340,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3349,7 +3367,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119836200</v>
+        <v>119840374</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3385,14 +3403,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491170</v>
+        <v>490963</v>
       </c>
       <c r="R26" t="n">
-        <v>6942951</v>
+        <v>6943253</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3424,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3434,7 +3452,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119837487</v>
+        <v>119839540</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,34 +3495,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491110</v>
+        <v>490872</v>
       </c>
       <c r="R27" t="n">
-        <v>6942959</v>
+        <v>6943080</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3536,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3546,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3573,7 +3591,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834113</v>
+        <v>119839263</v>
       </c>
       <c r="B28" t="n">
         <v>74654</v>
@@ -3609,14 +3627,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491239</v>
+        <v>490923</v>
       </c>
       <c r="R28" t="n">
-        <v>6942931</v>
+        <v>6943060</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3648,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3658,7 +3676,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3685,10 +3703,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119836355</v>
+        <v>119834398</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3701,21 +3719,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3725,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491146</v>
+        <v>491234</v>
       </c>
       <c r="R29" t="n">
-        <v>6942933</v>
+        <v>6942911</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3760,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,7 +3788,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119844174</v>
+        <v>119838566</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3809,49 +3827,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491221</v>
+        <v>491070</v>
       </c>
       <c r="R30" t="n">
-        <v>6942905</v>
+        <v>6942988</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3878,14 +3897,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,10 +3936,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119836510</v>
+        <v>119844215</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3924,50 +3948,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491143</v>
+        <v>491220</v>
       </c>
       <c r="R31" t="n">
-        <v>6942954</v>
+        <v>6942894</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3994,19 +4017,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:01</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4033,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119839776</v>
+        <v>119838719</v>
       </c>
       <c r="B32" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4045,50 +4063,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490825</v>
+        <v>491033</v>
       </c>
       <c r="R32" t="n">
-        <v>6943132</v>
+        <v>6943021</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4135,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4145,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119839540</v>
+        <v>119834815</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,34 +4300,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490872</v>
+        <v>491212</v>
       </c>
       <c r="R34" t="n">
-        <v>6943080</v>
+        <v>6942907</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,7 +4396,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119844215</v>
+        <v>119844174</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4426,10 +4444,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491220</v>
+        <v>491221</v>
       </c>
       <c r="R35" t="n">
-        <v>6942894</v>
+        <v>6942905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,10 +4511,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119840179</v>
+        <v>119844232</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4505,41 +4523,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490932</v>
+        <v>491042</v>
       </c>
       <c r="R36" t="n">
-        <v>6943156</v>
+        <v>6942994</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,19 +4592,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>18:57</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119834531</v>
+        <v>119838814</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4617,47 +4638,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491220</v>
+        <v>491028</v>
       </c>
       <c r="R37" t="n">
-        <v>6942907</v>
+        <v>6943013</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4689,7 +4701,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4711,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838814</v>
+        <v>119844150</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4742,37 +4754,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491028</v>
+        <v>491277</v>
       </c>
       <c r="R38" t="n">
-        <v>6943013</v>
+        <v>6942954</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4799,27 +4814,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4838,10 +4844,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844232</v>
+        <v>119836200</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4854,45 +4860,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491042</v>
+        <v>491170</v>
       </c>
       <c r="R39" t="n">
-        <v>6942994</v>
+        <v>6942951</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4919,14 +4917,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4953,10 +4956,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119844195</v>
+        <v>119834064</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4969,45 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491210</v>
+        <v>491239</v>
       </c>
       <c r="R40" t="n">
-        <v>6942900</v>
+        <v>6942931</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5034,14 +5029,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5068,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119834064</v>
+        <v>119837487</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5084,34 +5084,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491239</v>
+        <v>491110</v>
       </c>
       <c r="R41" t="n">
-        <v>6942931</v>
+        <v>6942959</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119844195</v>
+        <v>119836355</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,45 +2457,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491210</v>
+        <v>491146</v>
       </c>
       <c r="R18" t="n">
-        <v>6942900</v>
+        <v>6942933</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,14 +2514,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119836355</v>
+        <v>119844195</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2572,37 +2569,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491146</v>
+        <v>491210</v>
       </c>
       <c r="R19" t="n">
-        <v>6942933</v>
+        <v>6942900</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,19 +2634,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4626,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119838814</v>
+        <v>119836200</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4642,34 +4642,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491028</v>
+        <v>491170</v>
       </c>
       <c r="R37" t="n">
-        <v>6943013</v>
+        <v>6942951</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4738,10 +4738,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119844150</v>
+        <v>119838814</v>
       </c>
       <c r="B38" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4754,40 +4754,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491277</v>
+        <v>491028</v>
       </c>
       <c r="R38" t="n">
-        <v>6942954</v>
+        <v>6943013</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4814,18 +4811,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4844,10 +4850,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119836200</v>
+        <v>119844150</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4860,37 +4866,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491170</v>
+        <v>491277</v>
       </c>
       <c r="R39" t="n">
-        <v>6942951</v>
+        <v>6942954</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,27 +4926,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119844195</v>
+        <v>119835443</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,45 +2569,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491210</v>
+        <v>491200</v>
       </c>
       <c r="R19" t="n">
-        <v>6942900</v>
+        <v>6942933</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,14 +2626,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119834531</v>
+        <v>119844174</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,50 +2677,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491220</v>
+        <v>491221</v>
       </c>
       <c r="R20" t="n">
-        <v>6942907</v>
+        <v>6942905</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2750,19 +2746,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119836510</v>
+        <v>119834398</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>74654</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2801,47 +2792,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491143</v>
+        <v>491234</v>
       </c>
       <c r="R21" t="n">
-        <v>6942954</v>
+        <v>6942911</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2873,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840179</v>
+        <v>119840374</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2922,25 +2904,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2932,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490932</v>
+        <v>490963</v>
       </c>
       <c r="R22" t="n">
-        <v>6943156</v>
+        <v>6943253</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2985,7 +2967,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2977,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3143,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119835443</v>
+        <v>119844232</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,37 +3141,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491200</v>
+        <v>491042</v>
       </c>
       <c r="R24" t="n">
-        <v>6942933</v>
+        <v>6942994</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3216,19 +3206,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:15</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,7 +3240,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119834113</v>
+        <v>119834166</v>
       </c>
       <c r="B25" t="n">
         <v>74654</v>
@@ -3295,10 +3280,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491239</v>
+        <v>491238</v>
       </c>
       <c r="R25" t="n">
-        <v>6942931</v>
+        <v>6942925</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3330,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,7 +3325,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119840374</v>
+        <v>119834815</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,34 +3368,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490963</v>
+        <v>491212</v>
       </c>
       <c r="R26" t="n">
-        <v>6943253</v>
+        <v>6942907</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3442,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3452,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839263</v>
+        <v>119844215</v>
       </c>
       <c r="B28" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,37 +3592,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490923</v>
+        <v>491220</v>
       </c>
       <c r="R28" t="n">
-        <v>6943060</v>
+        <v>6942894</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3664,19 +3657,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:22</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:22</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,10 +3691,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834398</v>
+        <v>119838566</v>
       </c>
       <c r="B29" t="n">
-        <v>74654</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,38 +3703,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491234</v>
+        <v>491070</v>
       </c>
       <c r="R29" t="n">
-        <v>6942911</v>
+        <v>6942988</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3778,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3788,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119838566</v>
+        <v>119844150</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,50 +3824,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491070</v>
+        <v>491277</v>
       </c>
       <c r="R30" t="n">
-        <v>6942988</v>
+        <v>6942954</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,27 +3888,18 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3936,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119844215</v>
+        <v>119836200</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3952,45 +3934,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491220</v>
+        <v>491170</v>
       </c>
       <c r="R31" t="n">
-        <v>6942894</v>
+        <v>6942951</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4017,14 +3991,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,10 +4030,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119838719</v>
+        <v>119839263</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,47 +4042,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491033</v>
+        <v>490923</v>
       </c>
       <c r="R32" t="n">
-        <v>6943021</v>
+        <v>6943060</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4135,7 +4105,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,7 +4115,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,10 +4142,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119834166</v>
+        <v>119838814</v>
       </c>
       <c r="B33" t="n">
-        <v>74654</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,34 +4158,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491238</v>
+        <v>491028</v>
       </c>
       <c r="R33" t="n">
-        <v>6942925</v>
+        <v>6943013</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4247,7 +4217,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,7 +4227,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119834815</v>
+        <v>119844195</v>
       </c>
       <c r="B34" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,37 +4270,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491212</v>
+        <v>491210</v>
       </c>
       <c r="R34" t="n">
-        <v>6942907</v>
+        <v>6942900</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,19 +4335,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:48</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,10 +4369,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119844174</v>
+        <v>119834064</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4412,45 +4385,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491221</v>
+        <v>491239</v>
       </c>
       <c r="R35" t="n">
-        <v>6942905</v>
+        <v>6942931</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4477,14 +4442,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,10 +4481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119844232</v>
+        <v>119834113</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4527,45 +4497,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491042</v>
+        <v>491239</v>
       </c>
       <c r="R36" t="n">
-        <v>6942994</v>
+        <v>6942931</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4592,14 +4554,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4626,10 +4593,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119836200</v>
+        <v>119836510</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,38 +4605,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491170</v>
+        <v>491143</v>
       </c>
       <c r="R37" t="n">
-        <v>6942951</v>
+        <v>6942954</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4701,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4711,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4738,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838814</v>
+        <v>119838719</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,38 +4726,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491028</v>
+        <v>491033</v>
       </c>
       <c r="R38" t="n">
-        <v>6943013</v>
+        <v>6943021</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4813,7 +4798,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4808,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119844150</v>
+        <v>119840179</v>
       </c>
       <c r="B39" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4862,44 +4847,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491277</v>
+        <v>490932</v>
       </c>
       <c r="R39" t="n">
-        <v>6942954</v>
+        <v>6943156</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4926,18 +4908,27 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4956,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119834064</v>
+        <v>119834531</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,38 +4959,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491239</v>
+        <v>491220</v>
       </c>
       <c r="R40" t="n">
-        <v>6942931</v>
+        <v>6942907</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840374</v>
+        <v>119839776</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,41 +2904,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490963</v>
+        <v>490825</v>
       </c>
       <c r="R22" t="n">
-        <v>6943253</v>
+        <v>6943132</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2967,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2977,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,10 +3013,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839776</v>
+        <v>119844232</v>
       </c>
       <c r="B23" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,50 +3025,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490825</v>
+        <v>491042</v>
       </c>
       <c r="R23" t="n">
-        <v>6943132</v>
+        <v>6942994</v>
       </c>
       <c r="S23" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3086,19 +3094,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>18:40</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119844232</v>
+        <v>119840374</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3141,45 +3144,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491042</v>
+        <v>490963</v>
       </c>
       <c r="R24" t="n">
-        <v>6942994</v>
+        <v>6943253</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3206,14 +3201,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119844195</v>
+        <v>119834113</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4270,45 +4270,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491210</v>
+        <v>491239</v>
       </c>
       <c r="R34" t="n">
-        <v>6942900</v>
+        <v>6942931</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4335,14 +4327,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119834064</v>
+        <v>119844195</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,37 +4382,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491239</v>
+        <v>491210</v>
       </c>
       <c r="R35" t="n">
-        <v>6942931</v>
+        <v>6942900</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,19 +4447,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:01</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4481,10 +4481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119834113</v>
+        <v>119834064</v>
       </c>
       <c r="B36" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4497,27 +4497,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119834531</v>
+        <v>119837487</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,47 +4959,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491220</v>
+        <v>491110</v>
       </c>
       <c r="R40" t="n">
-        <v>6942907</v>
+        <v>6942959</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5031,7 +5022,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,7 +5032,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5068,10 +5059,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119837487</v>
+        <v>119834531</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,38 +5071,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491110</v>
+        <v>491220</v>
       </c>
       <c r="R41" t="n">
-        <v>6942959</v>
+        <v>6942907</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5178,6 +5178,123 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121722338</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57510</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490980</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6943268</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5295,6 +5295,229 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126523686</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491009</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943221</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126523762</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>491009</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943221</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -5523,7 +5523,7 @@
         <v>126920477</v>
       </c>
       <c r="B45" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -5523,7 +5523,7 @@
         <v>126920477</v>
       </c>
       <c r="B45" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -5523,7 +5523,7 @@
         <v>126920477</v>
       </c>
       <c r="B45" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110655564</v>
+        <v>119839540</v>
       </c>
       <c r="B2" t="n">
-        <v>55975</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>storöravattnet, Svartnäset, Hackås, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491081</v>
+        <v>490872</v>
       </c>
       <c r="R2" t="n">
         <v>6943080</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Johansson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Johansson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119315960</v>
+        <v>119840179</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,40 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490983</v>
+        <v>490932</v>
       </c>
       <c r="R3" t="n">
-        <v>6943216</v>
+        <v>6943156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,56 +871,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119318552</v>
+        <v>119315724</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490958</v>
+        <v>491009</v>
       </c>
       <c r="R4" t="n">
-        <v>6943143</v>
+        <v>6943267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119315951</v>
+        <v>119315780</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,27 +1001,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490982</v>
+        <v>491020</v>
       </c>
       <c r="R5" t="n">
-        <v>6943199</v>
+        <v>6943260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,37 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119315992</v>
+        <v>119315960</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491009</v>
+        <v>490983</v>
       </c>
       <c r="R6" t="n">
-        <v>6943266</v>
+        <v>6943216</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,19 +1202,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119316085</v>
+        <v>119315974</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1277,14 +1236,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490988</v>
+        <v>491009</v>
       </c>
       <c r="R7" t="n">
-        <v>6943186</v>
+        <v>6943221</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,9 +1273,19 @@
           <t>2024-08-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,49 +1301,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119315938</v>
+        <v>119316037</v>
       </c>
       <c r="B8" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,14 +1347,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490954</v>
+        <v>490983</v>
       </c>
       <c r="R8" t="n">
-        <v>6943156</v>
+        <v>6943182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1384,9 @@
           <t>2024-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,31 +1402,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119315724</v>
+        <v>119316085</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1503,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491009</v>
+        <v>490988</v>
       </c>
       <c r="R9" t="n">
-        <v>6943267</v>
+        <v>6943186</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,47 +1515,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119315870</v>
+        <v>119316170</v>
       </c>
       <c r="B10" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1614,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490981</v>
+        <v>491003</v>
       </c>
       <c r="R10" t="n">
-        <v>6943230</v>
+        <v>6943188</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,6 +1597,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1676,19 +1616,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119316170</v>
+        <v>119318943</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1719,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491003</v>
+        <v>490988</v>
       </c>
       <c r="R11" t="n">
-        <v>6943188</v>
+        <v>6943035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,19 +1717,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119315780</v>
+        <v>119834064</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1816,22 +1746,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Långberget, Långberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491020</v>
+        <v>491239</v>
       </c>
       <c r="R12" t="n">
-        <v>6943260</v>
+        <v>6942931</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,12 +1782,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,38 +1806,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119315974</v>
+        <v>119835443</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1922,22 +1853,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491009</v>
+        <v>491200</v>
       </c>
       <c r="R13" t="n">
-        <v>6943221</v>
+        <v>6942933</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,22 +1889,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,38 +1913,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119318943</v>
+        <v>119836200</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2038,22 +1960,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490988</v>
+        <v>491170</v>
       </c>
       <c r="R14" t="n">
-        <v>6943035</v>
+        <v>6942951</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,12 +1996,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,84 +2020,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119318886</v>
+        <v>119840374</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490972</v>
+        <v>490963</v>
       </c>
       <c r="R15" t="n">
-        <v>6943048</v>
+        <v>6943253</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,17 +2103,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,27 +2133,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119316037</v>
+        <v>119315938</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,21 +2156,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,14 +2179,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490983</v>
+        <v>490954</v>
       </c>
       <c r="R16" t="n">
-        <v>6943182</v>
+        <v>6943156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,9 +2216,19 @@
           <t>2024-08-24</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,68 +2244,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119318476</v>
+        <v>119834113</v>
       </c>
       <c r="B17" t="n">
-        <v>77866</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>lilltjärn, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490947</v>
+        <v>491239</v>
       </c>
       <c r="R17" t="n">
-        <v>6943144</v>
+        <v>6942931</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,12 +2321,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,34 +2345,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119836355</v>
+        <v>119834166</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,21 +2374,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491146</v>
+        <v>491238</v>
       </c>
       <c r="R18" t="n">
-        <v>6942933</v>
+        <v>6942925</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2516,7 +2433,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2443,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,15 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119835443</v>
+        <v>119834398</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,21 +2481,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491200</v>
+        <v>491234</v>
       </c>
       <c r="R19" t="n">
-        <v>6942933</v>
+        <v>6942911</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2628,7 +2540,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2550,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,15 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119844174</v>
+        <v>119834815</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,45 +2588,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491221</v>
+        <v>491212</v>
       </c>
       <c r="R20" t="n">
-        <v>6942905</v>
+        <v>6942907</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,14 +2645,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,15 +2684,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119834398</v>
+        <v>119839263</v>
       </c>
       <c r="B21" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,14 +2715,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491234</v>
+        <v>490923</v>
       </c>
       <c r="R21" t="n">
-        <v>6942911</v>
+        <v>6943060</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2855,7 +2754,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2764,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,15 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839776</v>
+        <v>119318476</v>
       </c>
       <c r="B22" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,46 +2802,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6443</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490825</v>
+        <v>490947</v>
       </c>
       <c r="R22" t="n">
-        <v>6943132</v>
+        <v>6943144</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,22 +2859,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:40</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:40</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,33 +2873,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119844232</v>
+        <v>119315992</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,42 +2903,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491042</v>
+        <v>491009</v>
       </c>
       <c r="R23" t="n">
-        <v>6942994</v>
+        <v>6943266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3091,17 +2960,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,33 +2984,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119840374</v>
+        <v>119837487</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,34 +3014,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490963</v>
+        <v>491110</v>
       </c>
       <c r="R24" t="n">
-        <v>6943253</v>
+        <v>6942959</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3203,7 +3073,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,7 +3083,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,15 +3110,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119834166</v>
+        <v>119838814</v>
       </c>
       <c r="B25" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,34 +3121,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491238</v>
+        <v>491028</v>
       </c>
       <c r="R25" t="n">
-        <v>6942925</v>
+        <v>6943013</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3315,7 +3180,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,7 +3190,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,15 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834815</v>
+        <v>126523762</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,37 +3228,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491212</v>
+        <v>491009</v>
       </c>
       <c r="R26" t="n">
-        <v>6942907</v>
+        <v>6943221</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3422,22 +3282,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3452,27 +3317,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839540</v>
+        <v>119318886</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3340,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490872</v>
+        <v>490972</v>
       </c>
       <c r="R27" t="n">
-        <v>6943080</v>
+        <v>6943048</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3534,22 +3406,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:33</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:33</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,27 +3431,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119844215</v>
+        <v>119844174</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,10 +3486,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491220</v>
+        <v>491221</v>
       </c>
       <c r="R28" t="n">
-        <v>6942894</v>
+        <v>6942905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3691,62 +3553,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119838566</v>
+        <v>119844195</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491070</v>
+        <v>491210</v>
       </c>
       <c r="R29" t="n">
-        <v>6942988</v>
+        <v>6942900</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3773,19 +3629,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:32</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,15 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119844150</v>
+        <v>119844215</v>
       </c>
       <c r="B30" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,26 +3674,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3855,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491277</v>
+        <v>491220</v>
       </c>
       <c r="R30" t="n">
-        <v>6942954</v>
+        <v>6942894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3893,13 +3744,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3918,15 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119836200</v>
+        <v>119844232</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,37 +3784,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491170</v>
+        <v>491042</v>
       </c>
       <c r="R31" t="n">
-        <v>6942951</v>
+        <v>6942994</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3991,19 +3849,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:43</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,53 +3883,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119839263</v>
+        <v>119315870</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490923</v>
+        <v>490981</v>
       </c>
       <c r="R32" t="n">
-        <v>6943060</v>
+        <v>6943230</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,22 +3956,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:22</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:22</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,65 +3976,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119838814</v>
+        <v>119839776</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Stor-Öravattnet, Stor-Öravattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491028</v>
+        <v>490825</v>
       </c>
       <c r="R33" t="n">
-        <v>6943013</v>
+        <v>6943132</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4217,7 +4067,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4227,7 +4077,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4254,53 +4104,63 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119834113</v>
+        <v>126920477</v>
       </c>
       <c r="B34" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491239</v>
+        <v>490971</v>
       </c>
       <c r="R34" t="n">
-        <v>6942931</v>
+        <v>6943222</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,22 +4184,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,32 +4226,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119844195</v>
+        <v>110655533</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4399,28 +4254,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>avledningsbeteende</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storörevattnet, Jmt</t>
+          <t>storöravattnet, Svartnäset, Hackås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491210</v>
+        <v>491081</v>
       </c>
       <c r="R35" t="n">
-        <v>6942900</v>
+        <v>6943079</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4444,17 +4311,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,27 +4331,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Eva Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Eva Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119834064</v>
+        <v>121722338</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4497,37 +4354,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långberget, Långberget, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491239</v>
+        <v>490980</v>
       </c>
       <c r="R36" t="n">
-        <v>6942931</v>
+        <v>6943268</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4551,22 +4413,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,15 +4455,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119836510</v>
+        <v>119315951</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4626,29 +4483,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491143</v>
+        <v>490982</v>
       </c>
       <c r="R37" t="n">
-        <v>6942954</v>
+        <v>6943199</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4672,22 +4524,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4696,33 +4538,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838719</v>
+        <v>119834531</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4759,14 +4597,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491033</v>
+        <v>491220</v>
       </c>
       <c r="R38" t="n">
-        <v>6943021</v>
+        <v>6942907</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4798,7 +4636,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4808,7 +4646,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,50 +4673,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119840179</v>
+        <v>119836510</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Svarthålån, Svarthålån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490932</v>
+        <v>491143</v>
       </c>
       <c r="R39" t="n">
-        <v>6943156</v>
+        <v>6942954</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4910,7 +4752,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4920,7 +4762,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4947,50 +4789,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119837487</v>
+        <v>119838566</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491110</v>
+        <v>491070</v>
       </c>
       <c r="R40" t="n">
-        <v>6942959</v>
+        <v>6942988</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5022,7 +4868,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5032,7 +4878,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5059,15 +4905,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119834531</v>
+        <v>119838719</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5104,14 +4945,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarthålån, Svarthålån, Jmt</t>
+          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491220</v>
+        <v>491033</v>
       </c>
       <c r="R41" t="n">
-        <v>6942907</v>
+        <v>6943021</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5143,7 +4984,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,7 +4994,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5180,55 +5021,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121722338</v>
+        <v>126523686</v>
       </c>
       <c r="B42" t="n">
-        <v>57522</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
+          <t>Lilltjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490980</v>
+        <v>491009</v>
       </c>
       <c r="R42" t="n">
-        <v>6943268</v>
+        <v>6943221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5255,22 +5090,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,61 +5120,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126523686</v>
+        <v>119318552</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>lilltjärn, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491009</v>
+        <v>490958</v>
       </c>
       <c r="R43" t="n">
-        <v>6943221</v>
+        <v>6943143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5366,22 +5200,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,28 +5214,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126523762</v>
+        <v>119844150</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,34 +5244,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Jmt</t>
+          <t>Storörevattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491009</v>
+        <v>491277</v>
       </c>
       <c r="R44" t="n">
-        <v>6943221</v>
+        <v>6942954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5473,27 +5301,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>19:51</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>19:51</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,143 +5315,22 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>126920477</v>
-      </c>
-      <c r="B45" t="n">
-        <v>56855</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>490971</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6943222</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33076-2024 artfynd.xlsx
+++ b/artfynd/A 33076-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119840179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315960</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315974</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316085</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119316170</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318943</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834064</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119835443</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119836200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119840374</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315938</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834113</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834166</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2574,6 +2664,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834398</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834815</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2788,6 +2888,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839263</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318476</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,6 +3110,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315992</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119837487</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3214,6 +3334,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119838814</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3326,6 +3451,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126523762</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3440,6 +3570,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318886</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3550,6 +3685,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119844174</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3660,6 +3800,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119844195</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3770,6 +3915,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119844215</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3880,6 +4030,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119844232</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3985,6 +4140,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315870</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839776</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4223,6 +4388,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920477</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4340,6 +4510,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110655533</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4452,6 +4627,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121722338</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4554,6 +4734,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119315951</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4670,6 +4855,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834531</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4786,6 +4976,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119836510</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4902,6 +5097,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119838566</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5018,6 +5218,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119838719</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5129,6 +5334,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126523686</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5230,6 +5440,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318552</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5331,8 +5546,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119844150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>